--- a/public/report/Report_WORK_IT.xlsx
+++ b/public/report/Report_WORK_IT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saranrat\Documents\GitHub\SPC-IT-Department\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF408450-C5C0-4E17-8BD9-FB98370DDC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE33783-5F4B-4A94-AC96-6E3A9D37EFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="917" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1378,13 +1378,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8938,10 +8938,7 @@
         <f>COUNTIF(L4:L305, 1)</f>
         <v>0</v>
       </c>
-      <c r="M307" s="24">
-        <f>COUNTA(M4:M305)-L308</f>
-        <v>0</v>
-      </c>
+      <c r="M307" s="24"/>
       <c r="N307" s="48">
         <f>SUM(SUMIFS(N4:N305,K4:K305,1),SUMIFS(N4:N305,L4:L305,1))</f>
         <v>0</v>
@@ -9968,30 +9965,30 @@
     <row r="22" spans="2:25" ht="15" thickBot="1"/>
     <row r="23" spans="2:25" ht="15.6" thickTop="1" thickBot="1">
       <c r="B23" s="8"/>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71" t="s">
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71" t="s">
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71" t="s">
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
     </row>
     <row r="24" spans="2:25" ht="24.6" thickTop="1" thickBot="1">
       <c r="B24" s="9" t="s">
@@ -10046,13 +10043,13 @@
         <v>15</v>
       </c>
       <c r="T24" s="17"/>
-      <c r="U24" s="69" t="s">
+      <c r="U24" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="V24" s="69"/>
-      <c r="W24" s="69"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="69"/>
+      <c r="V24" s="70"/>
+      <c r="W24" s="70"/>
+      <c r="X24" s="70"/>
+      <c r="Y24" s="70"/>
     </row>
     <row r="25" spans="2:25" ht="24.6" thickTop="1" thickBot="1">
       <c r="B25" s="9" t="s">
@@ -10075,13 +10072,13 @@
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
       <c r="T25" s="12"/>
-      <c r="U25" s="70" t="s">
+      <c r="U25" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="V25" s="70"/>
-      <c r="W25" s="70"/>
-      <c r="X25" s="70"/>
-      <c r="Y25" s="70"/>
+      <c r="V25" s="71"/>
+      <c r="W25" s="71"/>
+      <c r="X25" s="71"/>
+      <c r="Y25" s="71"/>
     </row>
     <row r="26" spans="2:25" ht="24.6" thickTop="1" thickBot="1">
       <c r="B26" s="9" t="s">
@@ -10191,11 +10188,6 @@
     <row r="31" spans="2:25" ht="15" thickTop="1"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B19:M19"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="U24:Y24"/>
     <mergeCell ref="U25:Y25"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -10211,6 +10203,11 @@
     <mergeCell ref="B17:N17"/>
     <mergeCell ref="B18:N18"/>
     <mergeCell ref="O1:R1"/>
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="U24:Y24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/public/report/Report_WORK_IT.xlsx
+++ b/public/report/Report_WORK_IT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saranrat\Documents\GitHub\SPC-IT-Department\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE33783-5F4B-4A94-AC96-6E3A9D37EFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2D27BF-2DD5-4499-BF2C-1B3E7DE20183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="917" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,6 +222,12 @@
     <t>เวลารวม</t>
   </si>
   <si>
+    <t>งาน</t>
+  </si>
+  <si>
+    <t>งานประจำ</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -230,9 +236,9 @@
         <rFont val="TH Sarabun New"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">    รหัสเอกสาร : QF-ICT-001
+      <t xml:space="preserve">    รหัสเอกสาร : IT-1234Eiei
     ครั้งที่แก้ไข : 00
-    วันที่มีผลบังคับใช้ : 04/01/2559</t>
+    วันที่มีผลบังคับใช้ : 01/01/2570</t>
     </r>
     <r>
       <rPr>
@@ -245,12 +251,6 @@
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>งาน</t>
-  </si>
-  <si>
-    <t>งานประจำ</t>
   </si>
 </sst>
 </file>
@@ -1378,13 +1378,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1564,52 +1564,6 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>282351</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>120411</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>264659</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>809897</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="282351" y="120411"/>
-          <a:ext cx="687158" cy="689486"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -4012,7 +3966,7 @@
       <c r="H1" s="58"/>
       <c r="I1" s="59"/>
       <c r="J1" s="60" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K1" s="61"/>
       <c r="L1" s="61"/>
@@ -8946,11 +8900,11 @@
     </row>
     <row r="308" spans="1:14" ht="23.4">
       <c r="K308" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L308" s="42"/>
       <c r="M308" s="45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N308" s="49"/>
     </row>
@@ -8964,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="N309" s="34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -9965,30 +9919,30 @@
     <row r="22" spans="2:25" ht="15" thickBot="1"/>
     <row r="23" spans="2:25" ht="15.6" thickTop="1" thickBot="1">
       <c r="B23" s="8"/>
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69" t="s">
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69" t="s">
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="L23" s="69"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="69" t="s">
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
     </row>
     <row r="24" spans="2:25" ht="24.6" thickTop="1" thickBot="1">
       <c r="B24" s="9" t="s">
@@ -10043,13 +9997,13 @@
         <v>15</v>
       </c>
       <c r="T24" s="17"/>
-      <c r="U24" s="70" t="s">
+      <c r="U24" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="V24" s="70"/>
-      <c r="W24" s="70"/>
-      <c r="X24" s="70"/>
-      <c r="Y24" s="70"/>
+      <c r="V24" s="71"/>
+      <c r="W24" s="71"/>
+      <c r="X24" s="71"/>
+      <c r="Y24" s="71"/>
     </row>
     <row r="25" spans="2:25" ht="24.6" thickTop="1" thickBot="1">
       <c r="B25" s="9" t="s">
@@ -10072,13 +10026,13 @@
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
       <c r="T25" s="12"/>
-      <c r="U25" s="71" t="s">
+      <c r="U25" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="V25" s="71"/>
-      <c r="W25" s="71"/>
-      <c r="X25" s="71"/>
-      <c r="Y25" s="71"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="69"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
     </row>
     <row r="26" spans="2:25" ht="24.6" thickTop="1" thickBot="1">
       <c r="B26" s="9" t="s">
@@ -10188,6 +10142,10 @@
     <row r="31" spans="2:25" ht="15" thickTop="1"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="U24:Y24"/>
     <mergeCell ref="U25:Y25"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -10204,10 +10162,6 @@
     <mergeCell ref="B18:N18"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="B19:M19"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="U24:Y24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
